--- a/teacher_import_demo.xlsx
+++ b/teacher_import_demo.xlsx
@@ -458,19 +458,21 @@
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="112" customHeight="1">
+    <row r="1" ht="140" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>填写说明：
 * 必填列。
 登录账号(工号)：租户内唯一，已存在则跳过。
 密码：长度至少 8 位，且需同时包含字母和数字。
-所属组织节点：填写系统中已存在的组织节点名称，匹配则关联，不匹配则忽略。
+所属组织节点(路径)：填写系统中已存在的组织节点完整路径，可自动匹配末级节点。
+  示例：某某职业技术学院-信息工程学院，或使用 /、-&gt; 等分隔符。
+  若节点名称唯一，也可只写组织节点名称（如：信息工程学院）。
 职位：多个职位用逗号分隔，须与系统中已存在的职位名称一致，不匹配则忽略。
 状态：在职 / 离职 / 外聘 / 禁用，默认为在职。</t>
         </is>
@@ -494,7 +496,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>所属组织节点(名称)</t>
+          <t>所属组织节点(路径)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -526,7 +528,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>某某职业技术学院-信息工程学院</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -558,7 +560,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>某某职业技术学院-信息工程学院</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -590,7 +592,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>汽车工程学院</t>
+          <t>某某职业技术学院-汽车工程学院</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -622,7 +624,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>智能制造学院</t>
+          <t>某某职业技术学院-智能制造学院</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -654,7 +656,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>经济管理学院</t>
+          <t>某某职业技术学院-经济管理学院</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -686,7 +688,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>汽车工程学院</t>
+          <t>某某职业技术学院-汽车工程学院</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -718,7 +720,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>某某职业技术学院-信息工程学院</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -750,7 +752,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>智能制造学院</t>
+          <t>某某职业技术学院-智能制造学院</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
